--- a/01-进度计划/月度计划表/2026.09/电站污水电气9月度工作计划表_赖永江处.xlsx
+++ b/01-进度计划/月度计划表/2026.09/电站污水电气9月度工作计划表_赖永江处.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="14080"/>
+    <workbookView windowWidth="23150" windowHeight="14080"/>
   </bookViews>
   <sheets>
     <sheet name="月度计划明细表" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="83">
   <si>
     <r>
       <rPr>
@@ -157,6 +157,9 @@
     <t>变压器生产</t>
   </si>
   <si>
+    <t>完成</t>
+  </si>
+  <si>
     <t>滞后</t>
   </si>
   <si>
@@ -320,7 +323,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +360,19 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1166,137 +1182,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1307,12 +1323,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1320,6 +1342,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1377,6 +1402,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1389,71 +1417,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1877,1314 +1923,1310 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.3727272727273" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.6272727272727" style="3" customWidth="1"/>
-    <col min="4" max="4" width="29.6272727272727" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.5454545454545" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.3636363636364" style="3" customWidth="1"/>
-    <col min="7" max="7" width="16.4545454545455" style="3" customWidth="1"/>
-    <col min="8" max="11" width="14.6363636363636" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.5454545454545" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.5454545454545" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12" style="3" customWidth="1"/>
-    <col min="15" max="15" width="24" style="3" customWidth="1"/>
-    <col min="16" max="16" width="33.1272727272727" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.52727272727273" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.66363636363636" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.7545454545455" style="4" customWidth="1"/>
+    <col min="5" max="12" width="8.94545454545455" style="3" customWidth="1"/>
+    <col min="13" max="13" width="7.58181818181818" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.27272727272727" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8.46363636363636" style="3" customWidth="1"/>
+    <col min="16" max="16" width="25.9454545454545" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:16">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="8"/>
     </row>
     <row r="2" ht="23" customHeight="1" spans="1:16">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="11" t="s">
+      <c r="H2" s="15"/>
+      <c r="I2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="9" t="s">
+      <c r="J2" s="15"/>
+      <c r="K2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="13" t="s">
+      <c r="L2" s="13"/>
+      <c r="M2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="13" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1" spans="1:16">
-      <c r="A3" s="16" t="s">
+    <row r="3" ht="55" customHeight="1" spans="1:16">
+      <c r="A3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:16">
-      <c r="A4" s="19">
+    <row r="4" ht="28" customHeight="1" spans="1:16">
+      <c r="A4" s="22">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="23"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:16">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="21" t="s">
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="26"/>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:16">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="21"/>
-      <c r="P5" s="23"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:16">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="21" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="26"/>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:16">
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="22">
+      <c r="E6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="25">
         <v>90</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="N6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="21" t="s">
+      <c r="O6" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="23" t="s">
+      <c r="P6" s="26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:16">
-      <c r="A7" s="19">
+    <row r="7" ht="28" customHeight="1" spans="1:16">
+      <c r="A7" s="22">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="23"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:16">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="21" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="26"/>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:16">
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="23"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:16">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="21" t="s">
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="26"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:16">
+      <c r="A9" s="27"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22" t="s">
+      <c r="E9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="23"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:16">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="21" t="s">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22" t="s">
+      <c r="O9" s="24"/>
+      <c r="P9" s="26"/>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:16">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="M10" s="22">
+      <c r="L10" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="25">
         <v>95</v>
       </c>
-      <c r="N10" s="22" t="s">
+      <c r="N10" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" s="24"/>
+      <c r="P10" s="26"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:16">
+      <c r="A11" s="22">
+        <v>3</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="26"/>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:16">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:16">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="25">
+        <v>80</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="26"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:16">
+      <c r="A14" s="22">
+        <v>4</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="26"/>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:16">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="33"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:16">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="23">
+        <v>90</v>
+      </c>
+      <c r="N16" s="23"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="33"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:16">
+      <c r="A17" s="22">
+        <v>5</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O17" s="24"/>
+      <c r="P17" s="26"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="O18" s="34"/>
+      <c r="P18" s="35"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="36">
+        <v>100</v>
+      </c>
+      <c r="N19" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" s="34"/>
+      <c r="P19" s="35"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="O10" s="21"/>
-      <c r="P10" s="23"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:16">
-      <c r="A11" s="19">
-        <v>3</v>
-      </c>
-      <c r="B11" s="20" t="s">
+      <c r="M20" s="39">
+        <v>100</v>
+      </c>
+      <c r="N20" s="25"/>
+      <c r="O20" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="P20" s="40"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A21" s="27">
+        <v>6</v>
+      </c>
+      <c r="B21" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C21" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D21" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="40"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="40"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="39">
+        <v>50</v>
+      </c>
+      <c r="N23" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="23"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:16">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="22" t="s">
+      <c r="O23" s="39"/>
+      <c r="P23" s="40"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A24" s="27">
+        <v>7</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="21" t="s">
+      <c r="F24" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="40"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="30" customHeight="1" spans="1:16">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="H25" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="40"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="39">
+        <v>50</v>
+      </c>
+      <c r="N26" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="O26" s="39"/>
+      <c r="P26" s="40"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="27" customHeight="1" spans="1:16">
+      <c r="A27" s="41">
+        <v>8</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="40"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="29" customHeight="1" spans="1:16">
+      <c r="A28" s="41"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="40"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="29" customHeight="1" spans="1:16">
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="39">
+        <v>50</v>
+      </c>
+      <c r="N29" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="28" customHeight="1" spans="1:16">
+      <c r="A30" s="45">
+        <v>6</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O30" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P30" s="40"/>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="29" customHeight="1" spans="1:16">
+      <c r="A31" s="45">
+        <v>7</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="M31" s="39">
+        <v>100</v>
+      </c>
+      <c r="N31" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="O31" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P31" s="40"/>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A32" s="45">
+        <v>8</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
+      <c r="N32" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O32" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P32" s="40"/>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A33" s="45">
+        <v>9</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="O33" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P33" s="40"/>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A34" s="45">
+        <v>10</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="O34" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="P34" s="40" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A35" s="48"/>
+      <c r="B35" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="M35" s="49">
+        <v>95</v>
+      </c>
+      <c r="N35" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O35" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P35" s="51"/>
+    </row>
+    <row r="36" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A36" s="48"/>
+      <c r="B36" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="M36" s="49">
+        <v>90</v>
+      </c>
+      <c r="N36" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O36" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P36" s="51"/>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A37" s="48"/>
+      <c r="B37" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="M37" s="49">
+        <v>50</v>
+      </c>
+      <c r="N37" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O37" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P37" s="26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A38" s="48"/>
+      <c r="B38" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="M38" s="49">
+        <v>50</v>
+      </c>
+      <c r="N38" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O38" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P38" s="26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
+      <c r="A39" s="53">
+        <v>11</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="54"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="56"/>
+    </row>
+    <row r="40" s="2" customFormat="1" ht="20" customHeight="1" spans="1:16">
+      <c r="A40" s="57"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="59"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="59"/>
+      <c r="M40" s="59"/>
+      <c r="N40" s="59"/>
+      <c r="O40" s="59"/>
+      <c r="P40" s="59"/>
+    </row>
+    <row r="41" ht="32" customHeight="1" spans="1:16">
+      <c r="A41" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="62"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" spans="1:16">
+      <c r="A42" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="E42" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" s="66"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="66"/>
+      <c r="J42" s="67"/>
+    </row>
+    <row r="43" ht="32" customHeight="1" spans="1:16">
+      <c r="A43" s="68"/>
+      <c r="B43" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="P12" s="23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:16">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="22">
-        <v>80</v>
-      </c>
-      <c r="N13" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="21"/>
-      <c r="P13" s="23"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:16">
-      <c r="A14" s="19">
-        <v>4</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="20" t="s">
+      <c r="F43" s="70"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="71"/>
+    </row>
+    <row r="44" ht="32" customHeight="1" spans="1:16">
+      <c r="A44" s="68"/>
+      <c r="B44" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="23"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:16">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="P15" s="29"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:16">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="20">
-        <v>90</v>
-      </c>
-      <c r="N16" s="20"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="29"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:16">
-      <c r="A17" s="19">
-        <v>5</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="O17" s="21"/>
-      <c r="P17" s="23"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="O18" s="30"/>
-      <c r="P18" s="31"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="30">
-        <v>95</v>
-      </c>
-      <c r="N19" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="O19" s="30"/>
-      <c r="P19" s="31"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" s="33">
-        <v>100</v>
-      </c>
-      <c r="N20" s="22"/>
-      <c r="O20" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="P20" s="34"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A21" s="24">
-        <v>6</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="34"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="34"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="33">
-        <v>50</v>
-      </c>
-      <c r="N23" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="O23" s="33"/>
-      <c r="P23" s="34"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A24" s="24">
-        <v>7</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="34"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="H25" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="34"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="33">
-        <v>50</v>
-      </c>
-      <c r="N26" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="33"/>
-      <c r="P26" s="34"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A27" s="35">
-        <v>8</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="34"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="34"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="33">
-        <v>50</v>
-      </c>
-      <c r="N29" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="O29" s="33"/>
-      <c r="P29" s="34"/>
-    </row>
-    <row r="30" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A30" s="39">
-        <v>6</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="O30" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P30" s="34"/>
-    </row>
-    <row r="31" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A31" s="39">
-        <v>7</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="33">
-        <v>100</v>
-      </c>
-      <c r="N31" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P31" s="34"/>
-    </row>
-    <row r="32" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A32" s="39">
-        <v>8</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="O32" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P32" s="34"/>
-    </row>
-    <row r="33" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A33" s="39">
-        <v>9</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="O33" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P33" s="34"/>
-    </row>
-    <row r="34" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A34" s="39">
-        <v>10</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="O34" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="P34" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A35" s="42"/>
-      <c r="B35" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="M35" s="43">
-        <v>95</v>
-      </c>
-      <c r="N35" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O35" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P35" s="45"/>
-    </row>
-    <row r="36" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A36" s="42"/>
-      <c r="B36" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="M36" s="43">
-        <v>90</v>
-      </c>
-      <c r="N36" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P36" s="45"/>
-    </row>
-    <row r="37" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A37" s="42"/>
-      <c r="B37" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="L37" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M37" s="43">
-        <v>50</v>
-      </c>
-      <c r="N37" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O37" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P37" s="23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A38" s="42"/>
-      <c r="B38" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="L38" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M38" s="43">
-        <v>50</v>
-      </c>
-      <c r="N38" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O38" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P38" s="23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" ht="19" customHeight="1" spans="1:16">
-      <c r="A39" s="46">
-        <v>11</v>
-      </c>
-      <c r="B39" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="47"/>
-      <c r="J39" s="47"/>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
-      <c r="N39" s="47"/>
-      <c r="O39" s="47"/>
-      <c r="P39" s="48"/>
-    </row>
-    <row r="40" s="2" customFormat="1" ht="20" customHeight="1" spans="1:16">
-      <c r="A40" s="49"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="51"/>
-    </row>
-    <row r="41" ht="32" customHeight="1" spans="1:16">
-      <c r="A41" s="52" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-    </row>
-    <row r="42" ht="32" customHeight="1" spans="1:16">
-      <c r="A42" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="56"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="I42" s="56"/>
-      <c r="J42" s="57"/>
-    </row>
-    <row r="43" ht="32" customHeight="1" spans="1:16">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="58" t="s">
-        <v>79</v>
-      </c>
-      <c r="E43" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="F43" s="60"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="60"/>
-      <c r="J43" s="61"/>
-    </row>
-    <row r="44" ht="32" customHeight="1" spans="1:16">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="E44" s="59" t="s">
+      <c r="D44" s="68" t="s">
         <v>81</v>
       </c>
-      <c r="F44" s="60"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="60"/>
-      <c r="J44" s="61"/>
+      <c r="E44" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" s="70"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
     </row>
     <row r="45" ht="32" customHeight="1"/>
   </sheetData>
